--- a/data/trans_orig/IP05A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A03-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>61392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74468</t>
+          <t>74526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>60361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72469</t>
+          <t>72258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>126232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143496</t>
+          <t>143932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44586</t>
+          <t>45039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338629</t>
+          <t>339087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363435</t>
+          <t>362507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>382504</t>
+          <t>382501</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409418</t>
+          <t>408013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731389</t>
+          <t>730654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>766145</t>
+          <t>765828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64131</t>
+          <t>63748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>58131</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82777</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>104806</t>
+          <t>105463</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135936</t>
+          <t>137554</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29786</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125117</t>
+          <t>124263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143473</t>
+          <t>142170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118917</t>
+          <t>119712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135521</t>
+          <t>135729</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248745</t>
+          <t>251469</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274119</t>
+          <t>274993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>24683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>41301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34368</t>
+          <t>33530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46708</t>
+          <t>46486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70846</t>
+          <t>68177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>537555</t>
+          <t>536907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>569528</t>
+          <t>570037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>576227</t>
+          <t>575683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>607912</t>
+          <t>607639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1122045</t>
+          <t>1122743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1168683</t>
+          <t>1168568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94741</t>
+          <t>95156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125645</t>
+          <t>124879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193321</t>
+          <t>193822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236155</t>
+          <t>236766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26136</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74772</t>
+          <t>74633</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85127</t>
+          <t>85230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68285</t>
+          <t>68286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78321</t>
+          <t>78687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146802</t>
+          <t>146887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161433</t>
+          <t>161730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27050</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388961</t>
+          <t>389486</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411359</t>
+          <t>411670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424800</t>
+          <t>427286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448729</t>
+          <t>449789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>825605</t>
+          <t>823352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>854787</t>
+          <t>855755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55891</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61492</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>76965</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>105577</t>
+          <t>108858</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,47 +3520,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>11258</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>17147</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>11258</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6890</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>17767</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133072</t>
+          <t>131263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148189</t>
+          <t>147762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137972</t>
+          <t>137760</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153272</t>
+          <t>152438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>276007</t>
+          <t>275360</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296832</t>
+          <t>297180</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>30804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50710</t>
+          <t>50597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>609691</t>
+          <t>606861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>638790</t>
+          <t>636757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>643720</t>
+          <t>645666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673419</t>
+          <t>673659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1263347</t>
+          <t>1259950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1303359</t>
+          <t>1300773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85624</t>
+          <t>89376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65129</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93037</t>
+          <t>92129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130577</t>
+          <t>133821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169496</t>
+          <t>171967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29945</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52942</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50388</t>
+          <t>49718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61177</t>
+          <t>60917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97404</t>
+          <t>97762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111693</t>
+          <t>112097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22597</t>
+          <t>22626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>380316</t>
+          <t>379893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405757</t>
+          <t>405960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394278</t>
+          <t>394445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>420323</t>
+          <t>419958</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783308</t>
+          <t>782717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>819191</t>
+          <t>820173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>45230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67715</t>
+          <t>67289</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51387</t>
+          <t>51955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>75139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101663</t>
+          <t>102061</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133143</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27866</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>46485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142147</t>
+          <t>141940</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156252</t>
+          <t>156379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148843</t>
+          <t>149037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164646</t>
+          <t>164456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>297200</t>
+          <t>296333</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>317145</t>
+          <t>318103</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23627</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31221</t>
+          <t>31656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>50581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>577559</t>
+          <t>577506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>608914</t>
+          <t>606699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>605382</t>
+          <t>605307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>636797</t>
+          <t>637545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1191205</t>
+          <t>1192871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1237713</t>
+          <t>1236750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66127</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93280</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>81105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>110458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154226</t>
+          <t>155021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194852</t>
+          <t>193166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36041</t>
+          <t>36276</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,47 +6487,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>50621</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>41328</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>50621</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>39247</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>63105</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45731</t>
+          <t>45896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52827</t>
+          <t>52801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>44742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56029</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93499</t>
+          <t>93340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107646</t>
+          <t>107083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308555</t>
+          <t>324809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>428786</t>
+          <t>427991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471169</t>
+          <t>470694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492164</t>
+          <t>490993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>793397</t>
+          <t>780420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>912698</t>
+          <t>913589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148171</t>
+          <t>133159</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37697</t>
+          <t>36960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51495</t>
+          <t>51229</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172158</t>
+          <t>187487</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>126156</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138887</t>
+          <t>138924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158186</t>
+          <t>158048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>171508</t>
+          <t>171322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>288835</t>
+          <t>289516</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307067</t>
+          <t>307572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>509684</t>
+          <t>488058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>612621</t>
+          <t>612787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>687322</t>
+          <t>685248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>713034</t>
+          <t>713032</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1181727</t>
+          <t>1194894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1315168</t>
+          <t>1316579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141791</t>
+          <t>169473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78139</t>
+          <t>78757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216185</t>
+          <t>203538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">

--- a/data/trans_orig/IP05A03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A03-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66790</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59925</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72011</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>69,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>68309</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>61392</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74526</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>61105</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>74174</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>75,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>67,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>66790</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>60361</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>72258</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>77,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126232</t>
+          <t>125804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143932</t>
+          <t>143770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15282</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10506</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21520</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20906</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14767</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27886</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15561</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28571</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15282</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10043</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21184</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45039</t>
+          <t>45314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1124</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4554</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8270</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86174</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86174</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86174</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86174</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86174</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>396424</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>382383</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>409006</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>531</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>351868</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>339087</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>362507</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>339398</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>362682</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>396424</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>382501</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>408013</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730654</t>
+          <t>729777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765828</t>
+          <t>766342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>68801</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56518</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>81508</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17,14%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>52210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>42333</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>63748</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>42179</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>64372</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>12,59%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>68801</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>58131</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>81984</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>105463</t>
+          <t>104457</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>137554</t>
+          <t>138828</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -1410,67 +1410,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>10420</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6087</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17140</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>10769</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6156</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17171</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6298</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16726</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10420</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6061</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16684</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475645</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475645</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475645</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>626</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>414847</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>414847</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>414847</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>475645</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>475645</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>475645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>128364</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>119717</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>81,17%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>75,7%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>134428</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>124263</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>142170</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>125933</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>143187</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>77,78%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>71,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>128364</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>119712</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>135729</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>81,17%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251469</t>
+          <t>251320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274993</t>
+          <t>273998</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25780</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18977</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34529</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>31792</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24683</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41301</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23872</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>40609</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25780</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18631</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33530</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46486</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68177</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3994</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8040</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>6620</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12474</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3156</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12507</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3994</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172840</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172840</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172840</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>591580</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>574364</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>607485</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>84,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>830</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>554606</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>536907</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>570037</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>537823</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>571625</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>81,8%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>79,19%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>591580</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>575683</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>607639</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>82,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1122743</t>
+          <t>1122174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1168568</t>
+          <t>1169684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>109862</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>95557</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127195</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104908</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>90003</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121661</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>89675</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>120953</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>15,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>109862</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>95156</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>124879</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193822</t>
+          <t>192395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236766</t>
+          <t>237946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18516</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12157</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>25884</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18514</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26411</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>12410</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>26311</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>18516</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>12274</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25660</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48998</t>
+          <t>47313</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>719958</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>719958</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>719958</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>678027</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>678027</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>678027</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>719958</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>719958</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>719958</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74230</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67791</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>78684</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>78,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>80798</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>74633</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85230</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>74852</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>84920</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>88,21%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74230</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>68286</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>78687</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146887</t>
+          <t>146580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161730</t>
+          <t>161698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9212</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14718</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10108</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5915</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16560</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5984</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16363</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9212</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5252</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14885</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>27117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6989</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2750</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7074</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>438511</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>426468</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>449497</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>583</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>401805</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>389486</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>411670</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>389812</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>411471</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>438511</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>427286</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>449789</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823352</t>
+          <t>823326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855755</t>
+          <t>854972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>48209</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37644</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59898</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43824</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>55420</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>34292</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>54898</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>9,74%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>48209</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37764</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>59316</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76965</t>
+          <t>78716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108858</t>
+          <t>107636</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6978</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12350</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4280</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8165</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8677</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6978</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11936</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>493698</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>493698</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>493698</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>652</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>449909</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>449909</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>449909</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>493698</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>493698</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>493698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>146161</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138022</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>152443</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>86,74%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>81,91%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>90,47%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>140999</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>131263</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147762</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>132861</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>148152</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>84,95%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>79,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>89,03%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>146161</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>137760</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>152438</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>86,74%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275360</t>
+          <t>276600</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>297180</t>
+          <t>297981</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21592</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15442</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30138</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18608</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12234</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26443</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12105</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25870</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21592</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15425</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30076</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50597</t>
+          <t>50895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3729</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>6362</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2966</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11637</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11499</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168500</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168500</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168500</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165970</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165970</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165970</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>168500</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>168500</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>168500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>658903</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>643684</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>673364</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>900</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>623603</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>606861</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>636757</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>608623</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>636673</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>88,14%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>85,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>658903</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>645666</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>673659</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>88,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1259950</t>
+          <t>1261143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1300773</t>
+          <t>1301978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>79013</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>66412</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>93437</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>72540</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>60812</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>89376</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>59986</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>86675</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,25%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>79013</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>66172</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>92129</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133821</t>
+          <t>133728</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171967</t>
+          <t>171400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10475</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5707</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16084</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>11337</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7024</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18307</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>10475</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6236</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>16788</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>748391</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>748391</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>748391</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>707480</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>707480</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>707480</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>748391</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>748391</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>748391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56483</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50274</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61015</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>48806</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43490</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53149</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>43914</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53157</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>82,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56483</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>49718</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60917</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97762</t>
+          <t>97068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112097</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -4951,67 +4951,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>8065</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4266</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13793</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>7876</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4007</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12944</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12593</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8065</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13318</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22626</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2695</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6433</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6871</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,54%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,83%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4066</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8235</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>408216</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>394478</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>421674</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>393946</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>379893</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>405960</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>380553</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>405685</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>83,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>408216</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>394445</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>419958</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>782717</t>
+          <t>783658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>820173</t>
+          <t>820666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -5402,107 +5402,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>62535</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50666</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>75514</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>55076</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>45230</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67289</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>44762</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>66807</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>11,73%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>62535</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>51955</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>75139</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>117611</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>102067</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>135433</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>10,68%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>117611</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>102061</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>135752</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15896</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10251</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23200</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>20325</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14312</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28357</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14605</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27549</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15896</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10194</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23191</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>27862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46485</t>
+          <t>46987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>486648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>486648</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>486648</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>469347</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>469347</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>469347</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>486648</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>486648</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>486648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157537</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149467</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164962</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>89,48%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150149</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>141940</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>156379</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>142690</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>156363</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>87,81%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>91,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157537</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149037</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>164456</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>296333</t>
+          <t>296044</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>318103</t>
+          <t>318140</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23509</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16684</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31274</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>16506</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11021</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23981</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10949</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23346</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,65%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23509</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16828</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31656</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50581</t>
+          <t>50153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8186</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4334</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8963</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1614</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8730</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3305</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7714</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184352</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184352</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184352</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184352</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184352</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184352</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>622237</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>604280</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>637573</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>84,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,7%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>592902</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>577506</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>606699</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>577697</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>607436</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>84,73%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>86,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>889</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>622237</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>605307</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>637545</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>84,13%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1192871</t>
+          <t>1192251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1236750</t>
+          <t>1238457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>94110</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>80240</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>109025</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>79458</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>65808</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93197</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>66778</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>93131</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>94110</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>81105</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>110458</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155021</t>
+          <t>153398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193166</t>
+          <t>194674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23267</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16413</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32915</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>27354</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20148</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>36276</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20047</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>36880</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23267</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>16688</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>31880</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41328</t>
+          <t>40915</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64265</t>
+          <t>64002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>739614</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>739614</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>739614</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>699714</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>699714</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>699714</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>739614</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>739614</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>739614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41592</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51541</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50275</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45896</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51516</t>
+          <t>42149</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44742</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56399</t>
+          <t>44735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>101791</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93340</t>
+          <t>82851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107083</t>
+          <t>94819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1798</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9440</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10268</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6084</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5846</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4345</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10513</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54248</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54248</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54248</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>445183</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>435646</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>453718</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>400181</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>324809</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>427991</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>482992</t>
+          <t>395030</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470694</t>
+          <t>381977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490993</t>
+          <t>404721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>883173</t>
+          <t>840213</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>780420</t>
+          <t>823547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>913589</t>
+          <t>852906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>24568</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17098</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>34226</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>54822</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>26889</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>133159</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>28,96%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>81480</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51229</t>
+          <t>44575</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187487</t>
+          <t>71841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8726</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4790</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10040</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>474055</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>474055</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>474055</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>459793</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>459793</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>459793</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514930</t>
+          <t>431697</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514930</t>
+          <t>431697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514930</t>
+          <t>431697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>974723</t>
+          <t>905751</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>974723</t>
+          <t>905751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>974723</t>
+          <t>905751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>152078</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>144670</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157251</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>86,88%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>133633</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>126156</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>138924</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>85,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165774</t>
+          <t>133742</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158048</t>
+          <t>125771</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>171322</t>
+          <t>139021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>299407</t>
+          <t>285820</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>289516</t>
+          <t>276262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307572</t>
+          <t>293975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10504</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6039</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16902</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9236</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15719</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18497</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3935</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8592</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2286</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10346</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10393</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4229</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1634</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8823</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166518</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166518</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166518</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>148143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>148143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>148143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181329</t>
+          <t>148515</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181329</t>
+          <t>148515</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181329</t>
+          <t>148515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>329472</t>
+          <t>315033</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>329472</t>
+          <t>315033</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>329472</t>
+          <t>315033</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>644604</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>631438</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>655056</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>862</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>584089</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>488058</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>612787</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>700282</t>
+          <t>570920</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>685248</t>
+          <t>556727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>713032</t>
+          <t>582911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1284371</t>
+          <t>1215525</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1194894</t>
+          <t>1193451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1316579</t>
+          <t>1230997</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>39517</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30634</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>50681</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>66037</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>37386</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>169473</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>43536</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56782</t>
+          <t>56459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>109639</t>
+          <t>83054</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>69678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>203538</t>
+          <t>101641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12656</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7584</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>21404</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>12058</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6935</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>19423</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>20278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>34932</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>696778</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>696778</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>696778</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>662184</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>662184</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>662184</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>757737</t>
+          <t>626600</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>757737</t>
+          <t>626600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>757737</t>
+          <t>626600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1419922</t>
+          <t>1323378</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1419922</t>
+          <t>1323378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1419922</t>
+          <t>1323378</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
